--- a/database schema.xlsx
+++ b/database schema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wesam/Desktop/thiqa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B827C263-D20F-D44C-8F21-7A96AF9C4260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DEDE79-DC19-1B46-86A2-DE747D9D20A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{D0E7EDB0-1383-5B41-B124-F3F8E63022FA}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="82">
-  <si>
-    <t>Customers</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="80">
   <si>
     <t>id</t>
   </si>
@@ -36,12 +33,6 @@
     <t>national_id</t>
   </si>
   <si>
-    <t>full_name_arabic</t>
-  </si>
-  <si>
-    <t>full_name_english</t>
-  </si>
-  <si>
     <t>city</t>
   </si>
   <si>
@@ -54,21 +45,12 @@
     <t>created_at</t>
   </si>
   <si>
-    <t>customer_id</t>
-  </si>
-  <si>
     <t>amount_paid</t>
   </si>
   <si>
     <t>payment_date</t>
   </si>
   <si>
-    <t>customer</t>
-  </si>
-  <si>
-    <t>Merchants</t>
-  </si>
-  <si>
     <t>business_name_ar</t>
   </si>
   <si>
@@ -114,9 +96,6 @@
     <t>trust_level</t>
   </si>
   <si>
-    <t>credit_accounts</t>
-  </si>
-  <si>
     <t>user_id</t>
   </si>
   <si>
@@ -141,12 +120,6 @@
     <t>due_date</t>
   </si>
   <si>
-    <t>Payment_events</t>
-  </si>
-  <si>
-    <t>payment_event</t>
-  </si>
-  <si>
     <t>credit_account_id</t>
   </si>
   <si>
@@ -162,9 +135,6 @@
     <t>geo_long</t>
   </si>
   <si>
-    <t>credit_scores</t>
-  </si>
-  <si>
     <t>score_value</t>
   </si>
   <si>
@@ -180,9 +150,6 @@
     <t>explanation_json</t>
   </si>
   <si>
-    <t>devices</t>
-  </si>
-  <si>
     <t>device_fingerprint</t>
   </si>
   <si>
@@ -192,9 +159,6 @@
     <t>platform</t>
   </si>
   <si>
-    <t>user_devices</t>
-  </si>
-  <si>
     <t>device_id</t>
   </si>
   <si>
@@ -204,9 +168,6 @@
     <t>last_seen</t>
   </si>
   <si>
-    <t>user_references</t>
-  </si>
-  <si>
     <t>reference_name</t>
   </si>
   <si>
@@ -216,9 +177,6 @@
     <t>verified</t>
   </si>
   <si>
-    <t>audit_logs</t>
-  </si>
-  <si>
     <t>actor_type</t>
   </si>
   <si>
@@ -240,9 +198,6 @@
     <t>new_values</t>
   </si>
   <si>
-    <t>user_consents</t>
-  </si>
-  <si>
     <t>consent_type</t>
   </si>
   <si>
@@ -255,9 +210,6 @@
     <t>revoked_at</t>
   </si>
   <si>
-    <t>merchant_reporting_quality</t>
-  </si>
-  <si>
     <t>late_submission_rate</t>
   </si>
   <si>
@@ -267,18 +219,68 @@
     <t>fraud_flag_count</t>
   </si>
   <si>
-    <t>users_logins</t>
-  </si>
-  <si>
     <t>user_type</t>
+  </si>
+  <si>
+    <t>full_name_ar</t>
+  </si>
+  <si>
+    <t>full_name_en</t>
+  </si>
+  <si>
+    <t>USERS</t>
+  </si>
+  <si>
+    <t>MERCHANTS</t>
+  </si>
+  <si>
+    <t>CREDIT ACCOUNTS</t>
+  </si>
+  <si>
+    <t>DEVICES</t>
+  </si>
+  <si>
+    <t>USER_DEVICES</t>
+  </si>
+  <si>
+    <t>USER_LOGINS</t>
+  </si>
+  <si>
+    <t>USER_REFERENCES</t>
+  </si>
+  <si>
+    <t>MERCHANT_REPORTING_QUALITY</t>
+  </si>
+  <si>
+    <t>AUDIT_LOGS</t>
+  </si>
+  <si>
+    <t>CREDIT_SCORES</t>
+  </si>
+  <si>
+    <t>USER_CONSENTS</t>
+  </si>
+  <si>
+    <t>user_name</t>
+  </si>
+  <si>
+    <t>PAYMENT_EVENTS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -306,8 +308,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -622,408 +625,400 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172C38F3-CE97-DB44-9302-67586010F729}">
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
     <col min="5" max="5" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="23.83203125" customWidth="1"/>
     <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" customWidth="1"/>
+    <col min="13" max="13" width="19.1640625" customWidth="1"/>
     <col min="14" max="14" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
         <v>38</v>
       </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N1" t="s">
-        <v>39</v>
-      </c>
-      <c r="P1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" t="s">
-        <v>11</v>
-      </c>
-      <c r="P4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" t="s">
         <v>25</v>
-      </c>
-      <c r="K5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" t="s">
-        <v>10</v>
-      </c>
-      <c r="P5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" t="s">
-        <v>26</v>
       </c>
       <c r="K6" t="s">
         <v>32</v>
       </c>
-      <c r="N6" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
+        <v>60</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
       </c>
       <c r="K7" t="s">
         <v>33</v>
       </c>
-      <c r="N7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" t="s">
         <v>20</v>
+      </c>
+      <c r="I8" t="s">
+        <v>27</v>
       </c>
       <c r="K8" t="s">
         <v>34</v>
       </c>
-      <c r="N8" t="s">
-        <v>43</v>
-      </c>
-      <c r="P8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" t="s">
         <v>12</v>
       </c>
-      <c r="H9" t="s">
-        <v>5</v>
+      <c r="I9" t="s">
+        <v>28</v>
       </c>
       <c r="K9" t="s">
         <v>35</v>
       </c>
-      <c r="N9" t="s">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" t="s">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" t="s">
         <v>44</v>
       </c>
-      <c r="P9" t="s">
+      <c r="G21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" t="s">
+        <v>13</v>
+      </c>
+      <c r="K21" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" t="s">
+        <v>61</v>
+      </c>
+      <c r="K22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" t="s">
+        <v>62</v>
+      </c>
+      <c r="K23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
         <v>5</v>
       </c>
-      <c r="H10" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" t="s">
-        <v>36</v>
-      </c>
-      <c r="N10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H12" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="K13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="H18" t="s">
-        <v>51</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="G24" t="s">
+        <v>48</v>
+      </c>
+      <c r="I24" t="s">
+        <v>63</v>
+      </c>
+      <c r="K24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G25" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K26" t="s">
         <v>55</v>
       </c>
-      <c r="L18" t="s">
-        <v>59</v>
-      </c>
-      <c r="N18" t="s">
-        <v>63</v>
-      </c>
-      <c r="P18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="H19" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" t="s">
-        <v>1</v>
-      </c>
-      <c r="N19" t="s">
-        <v>1</v>
-      </c>
-      <c r="P19" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H20" t="s">
-        <v>52</v>
-      </c>
-      <c r="J20" t="s">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K27" t="s">
         <v>56</v>
       </c>
-      <c r="L20" t="s">
-        <v>30</v>
-      </c>
-      <c r="N20" t="s">
-        <v>64</v>
-      </c>
-      <c r="P20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" t="s">
-        <v>53</v>
-      </c>
-      <c r="J21" t="s">
-        <v>57</v>
-      </c>
-      <c r="L21" t="s">
-        <v>60</v>
-      </c>
-      <c r="N21" t="s">
-        <v>65</v>
-      </c>
-      <c r="P21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" t="s">
-        <v>58</v>
-      </c>
-      <c r="L22" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" t="s">
-        <v>66</v>
-      </c>
-      <c r="P22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" t="s">
-        <v>8</v>
-      </c>
-      <c r="L23" t="s">
-        <v>61</v>
-      </c>
-      <c r="N23" t="s">
-        <v>67</v>
-      </c>
-      <c r="P23" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>81</v>
-      </c>
-      <c r="L24" t="s">
-        <v>62</v>
-      </c>
-      <c r="N24" t="s">
-        <v>68</v>
-      </c>
-      <c r="P24" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="N25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="N26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="N27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H33" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H34" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H35" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H36" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="37" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H37" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="38" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H38" t="s">
-        <v>79</v>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K28" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
